--- a/ASC_dataset_metadata.xlsx
+++ b/ASC_dataset_metadata.xlsx
@@ -1,17 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="465">
   <si>
     <t>judits_naming</t>
   </si>
@@ -1373,18 +1381,24 @@
   </si>
   <si>
     <r>
-      <rPr/>
       <t xml:space="preserve">Files received from the host museum. </t>
     </r>
     <r>
       <rPr>
+        <u/>
+        <sz val="10"/>
         <color rgb="FF1155CC"/>
-        <u/>
+        <rFont val="Arial"/>
       </rPr>
       <t>https://collections.museumofthebible.org/artifacts/32220-codex-valmadonna-i</t>
     </r>
     <r>
-      <rPr/>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve"> </t>
     </r>
   </si>
@@ -1425,131 +1439,142 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="26">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF1A1918"/>
       <name val="&quot;Sharp Grotesk&quot;"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="-webkit-standard"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
+      <name val="Arial"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF1A1918"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF1A1918"/>
       <name val="&quot;Quattrocento Sans&quot;"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF363636"/>
       <name val="&quot;Noto Sans&quot;"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF3A3A3A"/>
       <name val="&quot;Noto Sans&quot;"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="&quot;Sharp Grotesk&quot;"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF3A3A3A"/>
       <name val="&quot;Noto Sans&quot;"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="&quot;Helvetica Neue&quot;"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="&quot;Quattrocento Sans&quot;"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="&quot;Quattrocento Sans&quot;"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Lato"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF555555"/>
       <name val="&quot;Noto Sans&quot;"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF333333"/>
       <name val="&quot;Roboto Condensed&quot;"/>
     </font>
     <font>
       <b/>
-      <sz val="9.0"/>
+      <sz val="9"/>
       <color rgb="FF535557"/>
       <name val="&quot;Open Sans&quot;"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
+      <name val="Arial"/>
     </font>
     <font>
       <u/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF1A1918"/>
       <name val="&quot;Quattrocento Sans&quot;"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF1155CC"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Roboto"/>
     </font>
@@ -1559,7 +1584,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1581,117 +1606,82 @@
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="31">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="2" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="24" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1881,26 +1871,29 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:G214"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="49.25"/>
-    <col customWidth="1" min="2" max="2" width="44.88"/>
-    <col customWidth="1" min="3" max="3" width="12.63"/>
-    <col customWidth="1" min="4" max="4" width="14.38"/>
-    <col customWidth="1" min="5" max="5" width="14.75"/>
-    <col customWidth="1" min="6" max="6" width="12.0"/>
-    <col customWidth="1" min="7" max="7" width="70.88"/>
+    <col min="1" max="1" width="49.28515625" customWidth="1"/>
+    <col min="2" max="2" width="44.85546875" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="70.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1923,7 +1916,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:7">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
@@ -1931,7 +1924,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="4">
-        <v>1286.0</v>
+        <v>1286</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
@@ -1942,7 +1935,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:7">
       <c r="F3" s="1" t="s">
         <v>11</v>
       </c>
@@ -1950,7 +1943,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:7">
       <c r="F4" s="1" t="s">
         <v>13</v>
       </c>
@@ -1958,7 +1951,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:7">
       <c r="F5" s="1" t="s">
         <v>15</v>
       </c>
@@ -1966,7 +1959,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:7">
       <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
@@ -1974,7 +1967,7 @@
         <v>18</v>
       </c>
       <c r="C6" s="4">
-        <v>1216.0</v>
+        <v>1216</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1" t="s">
@@ -1987,7 +1980,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:7">
       <c r="F7" s="1" t="s">
         <v>22</v>
       </c>
@@ -1995,7 +1988,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:7">
       <c r="F8" s="1" t="s">
         <v>24</v>
       </c>
@@ -2003,7 +1996,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:7">
       <c r="F9" s="1" t="s">
         <v>26</v>
       </c>
@@ -2011,7 +2004,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:7">
       <c r="A10" s="6" t="s">
         <v>28</v>
       </c>
@@ -2019,7 +2012,7 @@
         <v>29</v>
       </c>
       <c r="C10" s="4">
-        <v>1303.0</v>
+        <v>1303</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>30</v>
@@ -2034,7 +2027,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:7">
       <c r="F11" s="1" t="s">
         <v>34</v>
       </c>
@@ -2042,7 +2035,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:7">
       <c r="F12" s="1" t="s">
         <v>36</v>
       </c>
@@ -2050,7 +2043,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:7">
       <c r="F13" s="1" t="s">
         <v>38</v>
       </c>
@@ -2058,7 +2051,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:7">
       <c r="A14" s="2" t="s">
         <v>40</v>
       </c>
@@ -2072,7 +2065,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:7">
       <c r="F15" s="1" t="s">
         <v>44</v>
       </c>
@@ -2080,7 +2073,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:7">
       <c r="F16" s="1" t="s">
         <v>46</v>
       </c>
@@ -2088,7 +2081,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:7">
       <c r="F17" s="1" t="s">
         <v>48</v>
       </c>
@@ -2096,7 +2089,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:7">
       <c r="A18" s="2" t="s">
         <v>50</v>
       </c>
@@ -2113,7 +2106,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:7">
       <c r="F19" s="1" t="s">
         <v>55</v>
       </c>
@@ -2121,7 +2114,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:7">
       <c r="F20" s="1" t="s">
         <v>57</v>
       </c>
@@ -2129,7 +2122,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:7">
       <c r="F21" s="1" t="s">
         <v>59</v>
       </c>
@@ -2137,7 +2130,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:7">
       <c r="A22" s="10" t="s">
         <v>61</v>
       </c>
@@ -2154,7 +2147,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:7">
       <c r="F23" s="1" t="s">
         <v>66</v>
       </c>
@@ -2162,7 +2155,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:7">
       <c r="F24" s="1" t="s">
         <v>68</v>
       </c>
@@ -2170,7 +2163,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:7">
       <c r="F25" s="1" t="s">
         <v>70</v>
       </c>
@@ -2178,7 +2171,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:7">
       <c r="A26" s="2" t="s">
         <v>72</v>
       </c>
@@ -2198,7 +2191,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:7">
       <c r="F27" s="1" t="s">
         <v>77</v>
       </c>
@@ -2206,7 +2199,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:7">
       <c r="F28" s="1" t="s">
         <v>79</v>
       </c>
@@ -2214,7 +2207,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:7">
       <c r="F29" s="1" t="s">
         <v>81</v>
       </c>
@@ -2222,7 +2215,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:7">
       <c r="A30" s="2" t="s">
         <v>83</v>
       </c>
@@ -2245,7 +2238,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:7">
       <c r="F31" s="1" t="s">
         <v>88</v>
       </c>
@@ -2253,7 +2246,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:7">
       <c r="F32" s="1" t="s">
         <v>90</v>
       </c>
@@ -2261,7 +2254,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:7">
       <c r="F33" s="1" t="s">
         <v>92</v>
       </c>
@@ -2269,7 +2262,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:7">
       <c r="A34" s="10" t="s">
         <v>94</v>
       </c>
@@ -2289,7 +2282,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:7">
       <c r="F35" s="1" t="s">
         <v>99</v>
       </c>
@@ -2297,7 +2290,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:7">
       <c r="F36" s="1" t="s">
         <v>101</v>
       </c>
@@ -2305,7 +2298,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:7">
       <c r="F37" s="1" t="s">
         <v>103</v>
       </c>
@@ -2313,7 +2306,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:7">
       <c r="A38" s="2" t="s">
         <v>105</v>
       </c>
@@ -2333,7 +2326,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:7">
       <c r="F39" s="1" t="s">
         <v>110</v>
       </c>
@@ -2341,7 +2334,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:7">
       <c r="F40" s="1" t="s">
         <v>112</v>
       </c>
@@ -2349,7 +2342,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:7">
       <c r="F41" s="1" t="s">
         <v>114</v>
       </c>
@@ -2357,7 +2350,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:7">
       <c r="A42" s="2" t="s">
         <v>116</v>
       </c>
@@ -2365,7 +2358,7 @@
         <v>117</v>
       </c>
       <c r="C42" s="1">
-        <v>1299.0</v>
+        <v>1299</v>
       </c>
       <c r="D42" s="11" t="s">
         <v>118</v>
@@ -2377,7 +2370,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:7">
       <c r="F43" s="1" t="s">
         <v>110</v>
       </c>
@@ -2385,7 +2378,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:7">
       <c r="F44" s="1" t="s">
         <v>108</v>
       </c>
@@ -2393,7 +2386,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:7">
       <c r="F45" s="1" t="s">
         <v>112</v>
       </c>
@@ -2401,7 +2394,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:7">
       <c r="A46" s="2" t="s">
         <v>124</v>
       </c>
@@ -2418,7 +2411,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:7">
       <c r="F47" s="1" t="s">
         <v>129</v>
       </c>
@@ -2426,7 +2419,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:7">
       <c r="F48" s="1" t="s">
         <v>131</v>
       </c>
@@ -2434,7 +2427,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:7">
       <c r="F49" s="1" t="s">
         <v>133</v>
       </c>
@@ -2442,7 +2435,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:7">
       <c r="A50" s="2" t="s">
         <v>135</v>
       </c>
@@ -2462,7 +2455,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:7">
       <c r="F51" s="1" t="s">
         <v>55</v>
       </c>
@@ -2470,7 +2463,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:7">
       <c r="F52" s="1" t="s">
         <v>59</v>
       </c>
@@ -2478,7 +2471,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:7">
       <c r="F53" s="1" t="s">
         <v>88</v>
       </c>
@@ -2486,7 +2479,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:7">
       <c r="A54" s="2" t="s">
         <v>141</v>
       </c>
@@ -2506,7 +2499,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:7">
       <c r="F55" s="1" t="s">
         <v>112</v>
       </c>
@@ -2514,7 +2507,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:7">
       <c r="F56" s="1" t="s">
         <v>108</v>
       </c>
@@ -2522,7 +2515,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:7">
       <c r="F57" s="1" t="s">
         <v>110</v>
       </c>
@@ -2530,7 +2523,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:7">
       <c r="A58" s="2" t="s">
         <v>148</v>
       </c>
@@ -2547,7 +2540,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:7">
       <c r="F59" s="1" t="s">
         <v>20</v>
       </c>
@@ -2555,7 +2548,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:7">
       <c r="F60" s="1" t="s">
         <v>22</v>
       </c>
@@ -2563,7 +2556,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:7">
       <c r="F61" s="1" t="s">
         <v>155</v>
       </c>
@@ -2571,7 +2564,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:7">
       <c r="A62" s="10" t="s">
         <v>157</v>
       </c>
@@ -2588,7 +2581,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:7">
       <c r="F63" s="1" t="s">
         <v>59</v>
       </c>
@@ -2596,7 +2589,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:7">
       <c r="F64" s="1" t="s">
         <v>88</v>
       </c>
@@ -2604,7 +2597,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:7">
       <c r="F65" s="1" t="s">
         <v>90</v>
       </c>
@@ -2612,7 +2605,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:7">
       <c r="A66" s="13" t="s">
         <v>163</v>
       </c>
@@ -2620,7 +2613,7 @@
         <v>164</v>
       </c>
       <c r="C66" s="1">
-        <v>1334.0</v>
+        <v>1334</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>96</v>
@@ -2632,7 +2625,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:7">
       <c r="F67" s="1" t="s">
         <v>119</v>
       </c>
@@ -2640,7 +2633,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:7">
       <c r="F68" s="1" t="s">
         <v>167</v>
       </c>
@@ -2648,7 +2641,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:7">
       <c r="F69" s="1" t="s">
         <v>20</v>
       </c>
@@ -2656,7 +2649,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:7">
       <c r="A70" s="13" t="s">
         <v>170</v>
       </c>
@@ -2676,7 +2669,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:7">
       <c r="F71" s="1" t="s">
         <v>36</v>
       </c>
@@ -2684,7 +2677,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:7">
       <c r="F72" s="1" t="s">
         <v>175</v>
       </c>
@@ -2692,7 +2685,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:7">
       <c r="F73" s="1" t="s">
         <v>177</v>
       </c>
@@ -2700,7 +2693,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:7">
       <c r="A74" s="13" t="s">
         <v>179</v>
       </c>
@@ -2717,7 +2710,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:7">
       <c r="F75" s="1" t="s">
         <v>112</v>
       </c>
@@ -2725,7 +2718,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:7">
       <c r="F76" s="1" t="s">
         <v>108</v>
       </c>
@@ -2733,7 +2726,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:7">
       <c r="F77" s="1" t="s">
         <v>110</v>
       </c>
@@ -2741,7 +2734,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:7">
       <c r="A78" s="13" t="s">
         <v>186</v>
       </c>
@@ -2758,7 +2751,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:7">
       <c r="F79" s="1" t="s">
         <v>70</v>
       </c>
@@ -2766,7 +2759,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:7">
       <c r="F80" s="1" t="s">
         <v>68</v>
       </c>
@@ -2774,7 +2767,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:7">
       <c r="F81" s="1" t="s">
         <v>66</v>
       </c>
@@ -2782,7 +2775,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:7">
       <c r="A82" s="13" t="s">
         <v>194</v>
       </c>
@@ -2802,7 +2795,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:7">
       <c r="F83" s="1" t="s">
         <v>198</v>
       </c>
@@ -2810,7 +2803,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:7">
       <c r="F84" s="1" t="s">
         <v>114</v>
       </c>
@@ -2818,7 +2811,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:7">
       <c r="F85" s="1" t="s">
         <v>112</v>
       </c>
@@ -2826,7 +2819,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:7">
       <c r="A86" s="13" t="s">
         <v>202</v>
       </c>
@@ -2834,7 +2827,7 @@
         <v>203</v>
       </c>
       <c r="C86" s="9">
-        <v>1302.0</v>
+        <v>1302</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>204</v>
@@ -2843,7 +2836,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:7">
       <c r="F87" s="1" t="s">
         <v>206</v>
       </c>
@@ -2851,7 +2844,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:7">
       <c r="F88" s="1" t="s">
         <v>208</v>
       </c>
@@ -2859,7 +2852,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:7">
       <c r="F89" s="1" t="s">
         <v>210</v>
       </c>
@@ -2867,7 +2860,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:7">
       <c r="A90" s="13" t="s">
         <v>212</v>
       </c>
@@ -2875,7 +2868,7 @@
         <v>213</v>
       </c>
       <c r="C90" s="9">
-        <v>1340.0</v>
+        <v>1340</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>114</v>
@@ -2884,7 +2877,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:7">
       <c r="F91" s="1" t="s">
         <v>112</v>
       </c>
@@ -2892,7 +2885,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:7">
       <c r="F92" s="1" t="s">
         <v>108</v>
       </c>
@@ -2900,7 +2893,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:7">
       <c r="F93" s="1" t="s">
         <v>110</v>
       </c>
@@ -2908,7 +2901,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:7">
       <c r="A94" s="13" t="s">
         <v>218</v>
       </c>
@@ -2928,7 +2921,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:7">
       <c r="F95" s="1" t="s">
         <v>198</v>
       </c>
@@ -2936,7 +2929,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:7">
       <c r="F96" s="1" t="s">
         <v>114</v>
       </c>
@@ -2944,7 +2937,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:7">
       <c r="F97" s="1" t="s">
         <v>112</v>
       </c>
@@ -2952,7 +2945,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:7">
       <c r="A98" s="13" t="s">
         <v>226</v>
       </c>
@@ -2972,7 +2965,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:7">
       <c r="F99" s="1" t="s">
         <v>90</v>
       </c>
@@ -2980,7 +2973,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:7">
       <c r="F100" s="1" t="s">
         <v>92</v>
       </c>
@@ -2988,7 +2981,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:7">
       <c r="F101" s="1" t="s">
         <v>231</v>
       </c>
@@ -2996,7 +2989,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="1:7">
       <c r="A102" s="13" t="s">
         <v>233</v>
       </c>
@@ -3004,13 +2997,13 @@
         <v>233</v>
       </c>
       <c r="C102" s="1">
-        <v>1193.0</v>
+        <v>1193</v>
       </c>
       <c r="G102" s="1" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:7">
       <c r="A103" s="15" t="s">
         <v>235</v>
       </c>
@@ -3018,7 +3011,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:7">
       <c r="A104" s="13" t="s">
         <v>237</v>
       </c>
@@ -3038,7 +3031,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:7">
       <c r="F105" s="1" t="s">
         <v>242</v>
       </c>
@@ -3046,7 +3039,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:7">
       <c r="F106" s="1" t="s">
         <v>244</v>
       </c>
@@ -3054,7 +3047,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="1:7">
       <c r="F107" s="1" t="s">
         <v>246</v>
       </c>
@@ -3062,7 +3055,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" spans="1:7">
       <c r="A108" s="13" t="s">
         <v>248</v>
       </c>
@@ -3079,7 +3072,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="1:7">
       <c r="F109" s="1" t="s">
         <v>253</v>
       </c>
@@ -3087,7 +3080,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="1:7">
       <c r="F110" s="1" t="s">
         <v>253</v>
       </c>
@@ -3095,7 +3088,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="1:7">
       <c r="F111" s="1" t="s">
         <v>255</v>
       </c>
@@ -3103,7 +3096,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" spans="1:7" ht="15.75" customHeight="1">
       <c r="A112" s="13" t="s">
         <v>257</v>
       </c>
@@ -3126,7 +3119,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="1:7" ht="15.75" customHeight="1">
       <c r="B113" s="18"/>
       <c r="F113" s="1" t="s">
         <v>59</v>
@@ -3135,7 +3128,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" spans="1:7">
       <c r="F114" s="1" t="s">
         <v>88</v>
       </c>
@@ -3143,7 +3136,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" spans="1:7">
       <c r="F115" s="1" t="s">
         <v>90</v>
       </c>
@@ -3151,7 +3144,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" spans="1:7">
       <c r="A116" s="10" t="s">
         <v>265</v>
       </c>
@@ -3171,7 +3164,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="1:7">
       <c r="F117" s="1" t="s">
         <v>270</v>
       </c>
@@ -3179,7 +3172,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" spans="1:7">
       <c r="F118" s="1" t="s">
         <v>272</v>
       </c>
@@ -3187,7 +3180,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" spans="1:7">
       <c r="F119" s="1" t="s">
         <v>274</v>
       </c>
@@ -3195,7 +3188,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" spans="1:7" ht="15.75" customHeight="1">
       <c r="A121" s="2" t="s">
         <v>276</v>
       </c>
@@ -3203,14 +3196,14 @@
         <v>277</v>
       </c>
       <c r="C121" s="19">
-        <v>1260.0</v>
+        <v>1260</v>
       </c>
       <c r="D121" s="1"/>
       <c r="G121" s="1" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" spans="1:7" ht="15.75" customHeight="1">
       <c r="A122" s="2" t="s">
         <v>279</v>
       </c>
@@ -3218,14 +3211,14 @@
         <v>280</v>
       </c>
       <c r="C122" s="19">
-        <v>1240.0</v>
+        <v>1240</v>
       </c>
       <c r="D122" s="1"/>
       <c r="G122" s="20" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" spans="1:7">
       <c r="A123" s="2" t="s">
         <v>281</v>
       </c>
@@ -3233,7 +3226,7 @@
         <v>282</v>
       </c>
       <c r="C123" s="1">
-        <v>1309.0</v>
+        <v>1309</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>283</v>
@@ -3245,7 +3238,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" spans="1:7">
       <c r="F124" s="1" t="s">
         <v>286</v>
       </c>
@@ -3253,7 +3246,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" spans="1:7">
       <c r="F125" s="1" t="s">
         <v>288</v>
       </c>
@@ -3261,7 +3254,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" spans="1:7">
       <c r="F126" s="1" t="s">
         <v>290</v>
       </c>
@@ -3269,7 +3262,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" spans="1:7">
       <c r="A127" s="2" t="s">
         <v>292</v>
       </c>
@@ -3280,37 +3273,37 @@
         <v>294</v>
       </c>
       <c r="F127" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="G127" s="5" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" spans="1:7">
       <c r="F128" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="G128" s="5" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" spans="1:7">
       <c r="F129" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="G129" s="5" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" spans="1:7">
       <c r="F130" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="G130" s="5" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" spans="1:7" ht="15.75" customHeight="1">
       <c r="A131" s="2" t="s">
         <v>299</v>
       </c>
@@ -3318,40 +3311,40 @@
         <v>300</v>
       </c>
       <c r="C131" s="1">
-        <v>1177.0</v>
+        <v>1177</v>
       </c>
       <c r="F131" s="1">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="G131" s="5" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" spans="1:7">
       <c r="F132" s="1">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="G132" s="5" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" spans="1:7">
       <c r="F133" s="1">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="G133" s="5" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" spans="1:7">
       <c r="F134" s="1">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="G134" s="5" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" spans="1:7">
       <c r="A135" s="2" t="s">
         <v>305</v>
       </c>
@@ -3359,7 +3352,7 @@
         <v>41</v>
       </c>
       <c r="C135" s="1">
-        <v>1300.0</v>
+        <v>1300</v>
       </c>
       <c r="D135" s="23" t="s">
         <v>306</v>
@@ -3374,7 +3367,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" spans="1:7">
       <c r="F136" s="1" t="s">
         <v>155</v>
       </c>
@@ -3382,7 +3375,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" spans="1:7">
       <c r="F137" s="1" t="s">
         <v>151</v>
       </c>
@@ -3390,7 +3383,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" spans="1:7">
       <c r="F138" s="1" t="s">
         <v>310</v>
       </c>
@@ -3398,7 +3391,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" spans="1:7">
       <c r="A139" s="3" t="s">
         <v>312</v>
       </c>
@@ -3406,58 +3399,58 @@
         <v>313</v>
       </c>
       <c r="C139" s="1">
-        <v>1237.0</v>
+        <v>1237</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>96</v>
       </c>
       <c r="F139" s="1">
-        <v>309.0</v>
+        <v>309</v>
       </c>
       <c r="G139" s="25" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" spans="1:7" ht="15.75" customHeight="1">
       <c r="A140" s="2"/>
       <c r="B140" s="17"/>
       <c r="C140" s="1"/>
       <c r="D140" s="17"/>
       <c r="E140" s="1"/>
       <c r="F140" s="1">
-        <v>306.0</v>
+        <v>306</v>
       </c>
       <c r="G140" s="5" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" spans="1:7" ht="15.75" customHeight="1">
       <c r="A141" s="2"/>
       <c r="B141" s="17"/>
       <c r="C141" s="1"/>
       <c r="D141" s="17"/>
       <c r="E141" s="1"/>
       <c r="F141" s="1">
-        <v>307.0</v>
+        <v>307</v>
       </c>
       <c r="G141" s="5" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" spans="1:7" ht="15.75" customHeight="1">
       <c r="A142" s="2"/>
       <c r="B142" s="17"/>
       <c r="C142" s="1"/>
       <c r="D142" s="17"/>
       <c r="E142" s="1"/>
       <c r="F142" s="1">
-        <v>308.0</v>
+        <v>308</v>
       </c>
       <c r="G142" s="5" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" spans="1:7" ht="15.75" customHeight="1">
       <c r="A143" s="2" t="s">
         <v>318</v>
       </c>
@@ -3465,7 +3458,7 @@
         <v>319</v>
       </c>
       <c r="C143" s="1">
-        <v>1296.0</v>
+        <v>1296</v>
       </c>
       <c r="D143" s="17" t="s">
         <v>320</v>
@@ -3477,7 +3470,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" spans="1:7" ht="15.75" customHeight="1">
       <c r="A144" s="2" t="s">
         <v>322</v>
       </c>
@@ -3485,7 +3478,7 @@
         <v>323</v>
       </c>
       <c r="C144" s="1">
-        <v>1342.0</v>
+        <v>1342</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>96</v>
@@ -3494,7 +3487,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" spans="1:7" ht="15.75" customHeight="1">
       <c r="A145" s="3" t="s">
         <v>324</v>
       </c>
@@ -3514,7 +3507,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" spans="1:7" ht="15.75" customHeight="1">
       <c r="A146" s="2" t="s">
         <v>328</v>
       </c>
@@ -3531,7 +3524,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" spans="1:7">
       <c r="A147" s="2" t="s">
         <v>331</v>
       </c>
@@ -3539,7 +3532,7 @@
         <v>332</v>
       </c>
       <c r="C147" s="1">
-        <v>1343.0</v>
+        <v>1343</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>96</v>
@@ -3548,7 +3541,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" spans="1:7">
       <c r="A148" s="2" t="s">
         <v>333</v>
       </c>
@@ -3556,7 +3549,7 @@
         <v>334</v>
       </c>
       <c r="C148" s="1">
-        <v>1233.0</v>
+        <v>1233</v>
       </c>
       <c r="D148" s="1" t="s">
         <v>335</v>
@@ -3571,7 +3564,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" spans="1:7">
       <c r="F149" s="1" t="s">
         <v>231</v>
       </c>
@@ -3579,7 +3572,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" spans="1:7">
       <c r="F150" s="1" t="s">
         <v>221</v>
       </c>
@@ -3587,7 +3580,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" spans="1:7">
       <c r="F151" s="1" t="s">
         <v>198</v>
       </c>
@@ -3595,7 +3588,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" spans="1:7">
       <c r="A152" s="10" t="s">
         <v>340</v>
       </c>
@@ -3603,7 +3596,7 @@
         <v>341</v>
       </c>
       <c r="C152" s="1">
-        <v>1343.0</v>
+        <v>1343</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>96</v>
@@ -3615,7 +3608,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" spans="1:7">
       <c r="F153" s="1" t="s">
         <v>114</v>
       </c>
@@ -3623,7 +3616,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" spans="1:7">
       <c r="F154" s="1" t="s">
         <v>112</v>
       </c>
@@ -3631,7 +3624,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" spans="1:7">
       <c r="F155" s="1" t="s">
         <v>108</v>
       </c>
@@ -3639,7 +3632,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" spans="1:7">
       <c r="A156" s="2" t="s">
         <v>346</v>
       </c>
@@ -3647,7 +3640,7 @@
         <v>347</v>
       </c>
       <c r="C156" s="1">
-        <v>1200.0</v>
+        <v>1200</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>96</v>
@@ -3659,7 +3652,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="157">
+    <row r="157" spans="1:7">
       <c r="F157" s="1" t="s">
         <v>350</v>
       </c>
@@ -3667,7 +3660,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" spans="1:7">
       <c r="F158" s="1" t="s">
         <v>352</v>
       </c>
@@ -3675,7 +3668,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" spans="1:7">
       <c r="F159" s="1" t="s">
         <v>354</v>
       </c>
@@ -3683,7 +3676,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" spans="1:7">
       <c r="A160" s="6" t="s">
         <v>356</v>
       </c>
@@ -3697,37 +3690,37 @@
         <v>96</v>
       </c>
       <c r="F160" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G160" s="5" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="161">
+    <row r="161" spans="1:7">
       <c r="F161" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G161" s="5" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" spans="1:7">
       <c r="F162" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="G162" s="5" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="163">
+    <row r="163" spans="1:7">
       <c r="F163" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="G163" s="5" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" spans="1:7">
       <c r="A164" s="2" t="s">
         <v>363</v>
       </c>
@@ -3738,37 +3731,37 @@
         <v>365</v>
       </c>
       <c r="F164" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G164" s="5" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" spans="1:7">
       <c r="F165" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G165" s="5" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" spans="1:7">
       <c r="F166" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="G166" s="5" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="167">
+    <row r="167" spans="1:7">
       <c r="F167" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="G167" s="5" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" spans="1:7">
       <c r="A168" s="2" t="s">
         <v>370</v>
       </c>
@@ -3779,37 +3772,37 @@
         <v>372</v>
       </c>
       <c r="F168" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="G168" s="5" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" spans="1:7">
       <c r="F169" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="G169" s="5" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" spans="1:7">
       <c r="F170" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="G170" s="5" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" spans="1:7">
       <c r="F171" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="G171" s="5" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" spans="1:7">
       <c r="A172" s="15" t="s">
         <v>377</v>
       </c>
@@ -3821,7 +3814,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="173">
+    <row r="173" spans="1:7">
       <c r="A173" s="2" t="s">
         <v>378</v>
       </c>
@@ -3841,7 +3834,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="174">
+    <row r="174" spans="1:7">
       <c r="F174" s="20" t="s">
         <v>382</v>
       </c>
@@ -3849,7 +3842,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="175">
+    <row r="175" spans="1:7">
       <c r="F175" s="1" t="s">
         <v>384</v>
       </c>
@@ -3857,7 +3850,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="176">
+    <row r="176" spans="1:7">
       <c r="F176" s="1" t="s">
         <v>386</v>
       </c>
@@ -3865,7 +3858,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="177">
+    <row r="177" spans="1:7">
       <c r="A177" s="2" t="s">
         <v>388</v>
       </c>
@@ -3876,40 +3869,43 @@
         <v>267</v>
       </c>
       <c r="F177" s="1">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="G177" s="5" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" spans="1:7">
       <c r="F178" s="1">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="G178" s="5" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="179">
+    <row r="179" spans="1:7">
       <c r="F179" s="1">
-        <v>32.0</v>
+        <v>32</v>
       </c>
       <c r="G179" s="5" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" spans="1:7">
       <c r="F180" s="1">
-        <v>66.0</v>
+        <v>66</v>
       </c>
       <c r="G180" s="5" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" spans="1:7">
       <c r="A181" s="2" t="s">
         <v>394</v>
       </c>
+      <c r="B181" t="s">
+        <v>394</v>
+      </c>
       <c r="C181" s="1" t="s">
         <v>395</v>
       </c>
@@ -3917,7 +3913,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="182">
+    <row r="182" spans="1:7">
       <c r="A182" s="2" t="s">
         <v>397</v>
       </c>
@@ -3934,7 +3930,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="183">
+    <row r="183" spans="1:7">
       <c r="F183" s="1" t="s">
         <v>402</v>
       </c>
@@ -3942,7 +3938,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="184">
+    <row r="184" spans="1:7">
       <c r="F184" s="1" t="s">
         <v>404</v>
       </c>
@@ -3950,7 +3946,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="185">
+    <row r="185" spans="1:7">
       <c r="F185" s="1" t="s">
         <v>406</v>
       </c>
@@ -3958,7 +3954,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="186">
+    <row r="186" spans="1:7">
       <c r="A186" s="2" t="s">
         <v>408</v>
       </c>
@@ -3975,7 +3971,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="187">
+    <row r="187" spans="1:7">
       <c r="F187" s="1" t="s">
         <v>412</v>
       </c>
@@ -3983,7 +3979,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="188">
+    <row r="188" spans="1:7">
       <c r="F188" s="1" t="s">
         <v>414</v>
       </c>
@@ -3991,7 +3987,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="189">
+    <row r="189" spans="1:7">
       <c r="F189" s="1" t="s">
         <v>416</v>
       </c>
@@ -3999,7 +3995,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="190">
+    <row r="190" spans="1:7">
       <c r="A190" s="2" t="s">
         <v>418</v>
       </c>
@@ -4016,7 +4012,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="191">
+    <row r="191" spans="1:7">
       <c r="F191" s="1" t="s">
         <v>423</v>
       </c>
@@ -4024,7 +4020,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="192">
+    <row r="192" spans="1:7">
       <c r="F192" s="1" t="s">
         <v>425</v>
       </c>
@@ -4032,7 +4028,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="193">
+    <row r="193" spans="1:7">
       <c r="F193" s="1" t="s">
         <v>427</v>
       </c>
@@ -4040,7 +4036,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="194">
+    <row r="194" spans="1:7">
       <c r="A194" s="2" t="s">
         <v>429</v>
       </c>
@@ -4057,7 +4053,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="195">
+    <row r="195" spans="1:7">
       <c r="F195" s="1" t="s">
         <v>433</v>
       </c>
@@ -4065,7 +4061,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="196">
+    <row r="196" spans="1:7">
       <c r="F196" s="1" t="s">
         <v>435</v>
       </c>
@@ -4073,7 +4069,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="197">
+    <row r="197" spans="1:7">
       <c r="F197" s="1" t="s">
         <v>437</v>
       </c>
@@ -4081,7 +4077,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="198">
+    <row r="198" spans="1:7">
       <c r="A198" s="2" t="s">
         <v>439</v>
       </c>
@@ -4089,7 +4085,7 @@
         <v>440</v>
       </c>
       <c r="C198" s="1">
-        <v>1296.0</v>
+        <v>1296</v>
       </c>
       <c r="E198" s="1" t="s">
         <v>441</v>
@@ -4101,7 +4097,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="199">
+    <row r="199" spans="1:7">
       <c r="F199" s="1" t="s">
         <v>444</v>
       </c>
@@ -4109,7 +4105,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="200">
+    <row r="200" spans="1:7">
       <c r="F200" s="1" t="s">
         <v>446</v>
       </c>
@@ -4117,7 +4113,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="201">
+    <row r="201" spans="1:7">
       <c r="F201" s="1" t="s">
         <v>448</v>
       </c>
@@ -4125,7 +4121,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="202">
+    <row r="202" spans="1:7">
       <c r="A202" s="2" t="s">
         <v>450</v>
       </c>
@@ -4133,43 +4129,43 @@
         <v>451</v>
       </c>
       <c r="C202" s="1">
-        <v>1189.0</v>
+        <v>1189</v>
       </c>
       <c r="E202" s="1" t="s">
         <v>452</v>
       </c>
       <c r="F202" s="1">
-        <v>146.0</v>
+        <v>146</v>
       </c>
       <c r="G202" s="25" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="203">
+    <row r="203" spans="1:7">
       <c r="A203" s="10"/>
       <c r="B203" s="13"/>
       <c r="F203" s="1">
-        <v>193.0</v>
+        <v>193</v>
       </c>
       <c r="G203" s="1"/>
     </row>
-    <row r="204">
+    <row r="204" spans="1:7">
       <c r="A204" s="10"/>
       <c r="B204" s="13"/>
       <c r="F204" s="1">
-        <v>197.0</v>
+        <v>197</v>
       </c>
       <c r="G204" s="1"/>
     </row>
-    <row r="205">
+    <row r="205" spans="1:7">
       <c r="A205" s="10"/>
       <c r="B205" s="13"/>
       <c r="F205" s="1">
-        <v>209.0</v>
+        <v>209</v>
       </c>
       <c r="G205" s="1"/>
     </row>
-    <row r="206">
+    <row r="206" spans="1:7">
       <c r="A206" s="10" t="s">
         <v>454</v>
       </c>
@@ -4183,22 +4179,22 @@
         <v>456</v>
       </c>
     </row>
-    <row r="207">
+    <row r="207" spans="1:7">
       <c r="F207" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="208">
+    <row r="208" spans="1:7">
       <c r="F208" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="209">
+    <row r="209" spans="1:7">
       <c r="F209" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="210">
+    <row r="210" spans="1:7">
       <c r="A210" s="2" t="s">
         <v>457</v>
       </c>
@@ -4206,7 +4202,7 @@
         <v>458</v>
       </c>
       <c r="C210" s="1">
-        <v>1215.0</v>
+        <v>1215</v>
       </c>
       <c r="D210" s="1" t="s">
         <v>459</v>
@@ -4221,17 +4217,17 @@
         <v>460</v>
       </c>
     </row>
-    <row r="211">
+    <row r="211" spans="1:7">
       <c r="F211" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="212">
+    <row r="212" spans="1:7">
       <c r="F212" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="213">
+    <row r="213" spans="1:7">
       <c r="A213" s="6"/>
       <c r="C213" s="1"/>
       <c r="D213" s="1"/>
@@ -4241,7 +4237,7 @@
       </c>
       <c r="G213" s="1"/>
     </row>
-    <row r="214">
+    <row r="214" spans="1:7">
       <c r="A214" s="30" t="s">
         <v>461</v>
       </c>
@@ -4249,7 +4245,7 @@
         <v>462</v>
       </c>
       <c r="C214" s="19">
-        <v>1284.0</v>
+        <v>1284</v>
       </c>
       <c r="D214" s="20" t="s">
         <v>463</v>
@@ -4263,187 +4259,187 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" location="d=[[PNX_MANUSCRIPTS990001204550205171-1,FL37460384]]" ref="G6"/>
-    <hyperlink r:id="rId2" location="d=[[PNX_MANUSCRIPTS990001204550205171-1,FL37460385]]" ref="G7"/>
-    <hyperlink r:id="rId3" location="d=[[PNX_MANUSCRIPTS990001204550205171-1,FL37460442]]" ref="G8"/>
-    <hyperlink r:id="rId4" location="d=[[PNX_MANUSCRIPTS990001204550205171-1,FL37460548]]" ref="G9"/>
-    <hyperlink r:id="rId5" ref="G15"/>
-    <hyperlink r:id="rId6" ref="G18"/>
-    <hyperlink r:id="rId7" ref="G19"/>
-    <hyperlink r:id="rId8" ref="G20"/>
-    <hyperlink r:id="rId9" ref="G21"/>
-    <hyperlink r:id="rId10" ref="G22"/>
-    <hyperlink r:id="rId11" ref="G23"/>
-    <hyperlink r:id="rId12" ref="G24"/>
-    <hyperlink r:id="rId13" ref="G25"/>
-    <hyperlink r:id="rId14" ref="G26"/>
-    <hyperlink r:id="rId15" ref="G27"/>
-    <hyperlink r:id="rId16" ref="G28"/>
-    <hyperlink r:id="rId17" ref="G29"/>
-    <hyperlink r:id="rId18" ref="G30"/>
-    <hyperlink r:id="rId19" ref="G31"/>
-    <hyperlink r:id="rId20" ref="G32"/>
-    <hyperlink r:id="rId21" ref="G33"/>
-    <hyperlink r:id="rId22" ref="G34"/>
-    <hyperlink r:id="rId23" ref="G35"/>
-    <hyperlink r:id="rId24" ref="G36"/>
-    <hyperlink r:id="rId25" ref="G37"/>
-    <hyperlink r:id="rId26" ref="G38"/>
-    <hyperlink r:id="rId27" ref="G39"/>
-    <hyperlink r:id="rId28" ref="G40"/>
-    <hyperlink r:id="rId29" ref="G41"/>
-    <hyperlink r:id="rId30" ref="G42"/>
-    <hyperlink r:id="rId31" ref="G43"/>
-    <hyperlink r:id="rId32" ref="G44"/>
-    <hyperlink r:id="rId33" ref="G45"/>
-    <hyperlink r:id="rId34" ref="G46"/>
-    <hyperlink r:id="rId35" ref="G47"/>
-    <hyperlink r:id="rId36" ref="G48"/>
-    <hyperlink r:id="rId37" ref="G49"/>
-    <hyperlink r:id="rId38" ref="G50"/>
-    <hyperlink r:id="rId39" ref="G51"/>
-    <hyperlink r:id="rId40" ref="G52"/>
-    <hyperlink r:id="rId41" ref="G53"/>
-    <hyperlink r:id="rId42" ref="G54"/>
-    <hyperlink r:id="rId43" ref="G55"/>
-    <hyperlink r:id="rId44" ref="G56"/>
-    <hyperlink r:id="rId45" ref="G57"/>
-    <hyperlink r:id="rId46" ref="G58"/>
-    <hyperlink r:id="rId47" ref="G59"/>
-    <hyperlink r:id="rId48" ref="G60"/>
-    <hyperlink r:id="rId49" ref="G61"/>
-    <hyperlink r:id="rId50" ref="G62"/>
-    <hyperlink r:id="rId51" ref="G63"/>
-    <hyperlink r:id="rId52" ref="G64"/>
-    <hyperlink r:id="rId53" ref="G65"/>
-    <hyperlink r:id="rId54" ref="G66"/>
-    <hyperlink r:id="rId55" ref="G67"/>
-    <hyperlink r:id="rId56" ref="G68"/>
-    <hyperlink r:id="rId57" ref="G69"/>
-    <hyperlink r:id="rId58" ref="G70"/>
-    <hyperlink r:id="rId59" ref="G71"/>
-    <hyperlink r:id="rId60" ref="G72"/>
-    <hyperlink r:id="rId61" ref="G73"/>
-    <hyperlink r:id="rId62" ref="G74"/>
-    <hyperlink r:id="rId63" ref="G75"/>
-    <hyperlink r:id="rId64" ref="G76"/>
-    <hyperlink r:id="rId65" ref="G77"/>
-    <hyperlink r:id="rId66" ref="G78"/>
-    <hyperlink r:id="rId67" ref="G79"/>
-    <hyperlink r:id="rId68" ref="G80"/>
-    <hyperlink r:id="rId69" ref="G81"/>
-    <hyperlink r:id="rId70" ref="G82"/>
-    <hyperlink r:id="rId71" ref="G83"/>
-    <hyperlink r:id="rId72" ref="G84"/>
-    <hyperlink r:id="rId73" ref="G85"/>
-    <hyperlink r:id="rId74" ref="G86"/>
-    <hyperlink r:id="rId75" ref="G87"/>
-    <hyperlink r:id="rId76" ref="G88"/>
-    <hyperlink r:id="rId77" ref="G89"/>
-    <hyperlink r:id="rId78" ref="G90"/>
-    <hyperlink r:id="rId79" ref="G91"/>
-    <hyperlink r:id="rId80" ref="G92"/>
-    <hyperlink r:id="rId81" ref="G93"/>
-    <hyperlink r:id="rId82" ref="G94"/>
-    <hyperlink r:id="rId83" ref="G95"/>
-    <hyperlink r:id="rId84" ref="G96"/>
-    <hyperlink r:id="rId85" ref="G97"/>
-    <hyperlink r:id="rId86" ref="G98"/>
-    <hyperlink r:id="rId87" ref="G99"/>
-    <hyperlink r:id="rId88" ref="G100"/>
-    <hyperlink r:id="rId89" ref="G101"/>
-    <hyperlink r:id="rId90" ref="G104"/>
-    <hyperlink r:id="rId91" ref="G105"/>
-    <hyperlink r:id="rId92" ref="G106"/>
-    <hyperlink r:id="rId93" ref="G107"/>
-    <hyperlink r:id="rId94" location="d=[[PNX_MANUSCRIPTS990000800110205171-1,FL50442639]]" ref="G108"/>
-    <hyperlink r:id="rId95" location="d=[[PNX_MANUSCRIPTS990000800110205171-1,FL50442638]]" ref="G109"/>
-    <hyperlink r:id="rId96" location="d=[[PNX_MANUSCRIPTS990000800110205171-1,FL50442638]]" ref="G110"/>
-    <hyperlink r:id="rId97" location="d=[[PNX_MANUSCRIPTS990000800110205171-1,FL50442738]]" ref="G111"/>
-    <hyperlink r:id="rId98" location="d=[[PNX_MANUSCRIPTS990001264630205171-2,FL48276986]]" ref="G112"/>
-    <hyperlink r:id="rId99" location="d=[[PNX_MANUSCRIPTS990001264630205171-2,FL48276991]]" ref="G113"/>
-    <hyperlink r:id="rId100" location="d=[[PNX_MANUSCRIPTS990001264630205171-2,FL48276997]]" ref="G114"/>
-    <hyperlink r:id="rId101" location="d=[[PNX_MANUSCRIPTS990001264630205171-2,FL48277003]]" ref="G115"/>
-    <hyperlink r:id="rId102" ref="G116"/>
-    <hyperlink r:id="rId103" ref="G117"/>
-    <hyperlink r:id="rId104" ref="G118"/>
-    <hyperlink r:id="rId105" ref="G119"/>
-    <hyperlink r:id="rId106" location="d=[[PNX_MANUSCRIPTS990001517870205171-1,FL49943073]]" ref="G123"/>
-    <hyperlink r:id="rId107" location="d=[[PNX_MANUSCRIPTS990001517870205171-1,FL49943074]]" ref="G124"/>
-    <hyperlink r:id="rId108" location="d=[[PNX_MANUSCRIPTS990001517870205171-1,FL49943075]]" ref="G125"/>
-    <hyperlink r:id="rId109" location="d=[[PNX_MANUSCRIPTS990001517870205171-1,FL49943611]]" ref="G126"/>
-    <hyperlink r:id="rId110" ref="G127"/>
-    <hyperlink r:id="rId111" ref="G128"/>
-    <hyperlink r:id="rId112" ref="G129"/>
-    <hyperlink r:id="rId113" ref="G130"/>
-    <hyperlink r:id="rId114" location="d=[[PNX_MANUSCRIPTS990001978950205171-1,FL50769309]]" ref="G131"/>
-    <hyperlink r:id="rId115" location="d=[[PNX_MANUSCRIPTS990001978950205171-1,FL50769310]]" ref="G132"/>
-    <hyperlink r:id="rId116" location="d=[[PNX_MANUSCRIPTS990001978950205171-1,FL50769311]]" ref="G133"/>
-    <hyperlink r:id="rId117" location="d=[[PNX_MANUSCRIPTS990001978950205171-1,FL50769312]]" ref="G134"/>
-    <hyperlink r:id="rId118" ref="G135"/>
-    <hyperlink r:id="rId119" ref="G136"/>
-    <hyperlink r:id="rId120" ref="G137"/>
-    <hyperlink r:id="rId121" ref="G138"/>
-    <hyperlink r:id="rId122" ref="G139"/>
-    <hyperlink r:id="rId123" ref="G140"/>
-    <hyperlink r:id="rId124" ref="G141"/>
-    <hyperlink r:id="rId125" ref="G142"/>
-    <hyperlink r:id="rId126" ref="G148"/>
-    <hyperlink r:id="rId127" ref="G149"/>
-    <hyperlink r:id="rId128" ref="G150"/>
-    <hyperlink r:id="rId129" ref="G151"/>
-    <hyperlink r:id="rId130" ref="G152"/>
-    <hyperlink r:id="rId131" ref="G153"/>
-    <hyperlink r:id="rId132" ref="G154"/>
-    <hyperlink r:id="rId133" ref="G155"/>
-    <hyperlink r:id="rId134" ref="G156"/>
-    <hyperlink r:id="rId135" ref="G157"/>
-    <hyperlink r:id="rId136" ref="G158"/>
-    <hyperlink r:id="rId137" ref="G159"/>
-    <hyperlink r:id="rId138" ref="G160"/>
-    <hyperlink r:id="rId139" ref="G161"/>
-    <hyperlink r:id="rId140" ref="G162"/>
-    <hyperlink r:id="rId141" ref="G163"/>
-    <hyperlink r:id="rId142" ref="G164"/>
-    <hyperlink r:id="rId143" ref="G165"/>
-    <hyperlink r:id="rId144" ref="G166"/>
-    <hyperlink r:id="rId145" ref="G167"/>
-    <hyperlink r:id="rId146" ref="G168"/>
-    <hyperlink r:id="rId147" ref="G169"/>
-    <hyperlink r:id="rId148" ref="G170"/>
-    <hyperlink r:id="rId149" ref="G171"/>
-    <hyperlink r:id="rId150" ref="G173"/>
-    <hyperlink r:id="rId151" ref="G174"/>
-    <hyperlink r:id="rId152" ref="G175"/>
-    <hyperlink r:id="rId153" ref="G176"/>
-    <hyperlink r:id="rId154" location="d=[[PNX_MANUSCRIPTS990025709670205171-1,FL14822146]]" ref="G177"/>
-    <hyperlink r:id="rId155" location="d=[[PNX_MANUSCRIPTS990025709670205171-1,FL14822227]]" ref="G178"/>
-    <hyperlink r:id="rId156" location="d=[[PNX_MANUSCRIPTS990025709670205171-1,FL14822061]]" ref="G179"/>
-    <hyperlink r:id="rId157" location="d=[[PNX_MANUSCRIPTS990025709670205171-1,FL14822187]]" ref="G180"/>
-    <hyperlink r:id="rId158" location="d=[[PNX_MANUSCRIPTS990000841690205171-1,FL13940557]]" ref="G182"/>
-    <hyperlink r:id="rId159" location="d=[[PNX_MANUSCRIPTS990000841690205171-1,FL13940568]]" ref="G183"/>
-    <hyperlink r:id="rId160" location="d=[[PNX_MANUSCRIPTS990000841690205171-1,FL13940717]]" ref="G184"/>
-    <hyperlink r:id="rId161" location="d=[[PNX_MANUSCRIPTS990000841690205171-1,FL13940405]]" ref="G185"/>
-    <hyperlink r:id="rId162" location="d=[[PNX_MANUSCRIPTS990000830080205171-1,FL21133815]]" ref="G186"/>
-    <hyperlink r:id="rId163" location="d=[[PNX_MANUSCRIPTS990000830080205171-1,FL21133862]]" ref="G187"/>
-    <hyperlink r:id="rId164" location="d=[[PNX_MANUSCRIPTS990000830080205171-1,FL21133861]]" ref="G188"/>
-    <hyperlink r:id="rId165" location="d=[[PNX_MANUSCRIPTS990000830080205171-1,FL21133823]]" ref="G189"/>
-    <hyperlink r:id="rId166" location="d=[[PNX_MANUSCRIPTS990000690070205171-1,FL21117134]]" ref="G190"/>
-    <hyperlink r:id="rId167" location="d=[[PNX_MANUSCRIPTS990000690070205171-1,FL21117057]]" ref="G191"/>
-    <hyperlink r:id="rId168" location="d=[[PNX_MANUSCRIPTS990000690070205171-1,FL21117713]]" ref="G192"/>
-    <hyperlink r:id="rId169" location="d=[[PNX_MANUSCRIPTS990000690070205171-1,FL21117069]]" ref="G193"/>
-    <hyperlink r:id="rId170" location="d=[[PNX_MANUSCRIPTS990000728040205171-1,FL22949894]]" ref="G194"/>
-    <hyperlink r:id="rId171" location="d=[[PNX_MANUSCRIPTS990000728040205171-1,FL22949849]]" ref="G195"/>
-    <hyperlink r:id="rId172" location="d=[[PNX_MANUSCRIPTS990000728040205171-1,FL22949980]]" ref="G196"/>
-    <hyperlink r:id="rId173" location="d=[[PNX_MANUSCRIPTS990000728040205171-1,FL22950162]]" ref="G197"/>
-    <hyperlink r:id="rId174" ref="G198"/>
-    <hyperlink r:id="rId175" ref="G199"/>
-    <hyperlink r:id="rId176" ref="G200"/>
-    <hyperlink r:id="rId177" ref="G201"/>
-    <hyperlink r:id="rId178" ref="G202"/>
-    <hyperlink r:id="rId179" ref="G206"/>
-    <hyperlink r:id="rId180" ref="G210"/>
+    <hyperlink ref="G6" r:id="rId1" location="d=[[PNX_MANUSCRIPTS990001204550205171-1,FL37460384]]"/>
+    <hyperlink ref="G7" r:id="rId2" location="d=[[PNX_MANUSCRIPTS990001204550205171-1,FL37460385]]"/>
+    <hyperlink ref="G8" r:id="rId3" location="d=[[PNX_MANUSCRIPTS990001204550205171-1,FL37460442]]"/>
+    <hyperlink ref="G9" r:id="rId4" location="d=[[PNX_MANUSCRIPTS990001204550205171-1,FL37460548]]"/>
+    <hyperlink ref="G15" r:id="rId5"/>
+    <hyperlink ref="G18" r:id="rId6"/>
+    <hyperlink ref="G19" r:id="rId7"/>
+    <hyperlink ref="G20" r:id="rId8"/>
+    <hyperlink ref="G21" r:id="rId9"/>
+    <hyperlink ref="G22" r:id="rId10"/>
+    <hyperlink ref="G23" r:id="rId11"/>
+    <hyperlink ref="G24" r:id="rId12"/>
+    <hyperlink ref="G25" r:id="rId13"/>
+    <hyperlink ref="G26" r:id="rId14"/>
+    <hyperlink ref="G27" r:id="rId15"/>
+    <hyperlink ref="G28" r:id="rId16"/>
+    <hyperlink ref="G29" r:id="rId17"/>
+    <hyperlink ref="G30" r:id="rId18"/>
+    <hyperlink ref="G31" r:id="rId19"/>
+    <hyperlink ref="G32" r:id="rId20"/>
+    <hyperlink ref="G33" r:id="rId21"/>
+    <hyperlink ref="G34" r:id="rId22"/>
+    <hyperlink ref="G35" r:id="rId23"/>
+    <hyperlink ref="G36" r:id="rId24"/>
+    <hyperlink ref="G37" r:id="rId25"/>
+    <hyperlink ref="G38" r:id="rId26"/>
+    <hyperlink ref="G39" r:id="rId27"/>
+    <hyperlink ref="G40" r:id="rId28"/>
+    <hyperlink ref="G41" r:id="rId29"/>
+    <hyperlink ref="G42" r:id="rId30"/>
+    <hyperlink ref="G43" r:id="rId31"/>
+    <hyperlink ref="G44" r:id="rId32"/>
+    <hyperlink ref="G45" r:id="rId33"/>
+    <hyperlink ref="G46" r:id="rId34"/>
+    <hyperlink ref="G47" r:id="rId35"/>
+    <hyperlink ref="G48" r:id="rId36"/>
+    <hyperlink ref="G49" r:id="rId37"/>
+    <hyperlink ref="G50" r:id="rId38"/>
+    <hyperlink ref="G51" r:id="rId39"/>
+    <hyperlink ref="G52" r:id="rId40"/>
+    <hyperlink ref="G53" r:id="rId41"/>
+    <hyperlink ref="G54" r:id="rId42"/>
+    <hyperlink ref="G55" r:id="rId43"/>
+    <hyperlink ref="G56" r:id="rId44"/>
+    <hyperlink ref="G57" r:id="rId45"/>
+    <hyperlink ref="G58" r:id="rId46"/>
+    <hyperlink ref="G59" r:id="rId47"/>
+    <hyperlink ref="G60" r:id="rId48"/>
+    <hyperlink ref="G61" r:id="rId49"/>
+    <hyperlink ref="G62" r:id="rId50"/>
+    <hyperlink ref="G63" r:id="rId51"/>
+    <hyperlink ref="G64" r:id="rId52"/>
+    <hyperlink ref="G65" r:id="rId53"/>
+    <hyperlink ref="G66" r:id="rId54"/>
+    <hyperlink ref="G67" r:id="rId55"/>
+    <hyperlink ref="G68" r:id="rId56"/>
+    <hyperlink ref="G69" r:id="rId57"/>
+    <hyperlink ref="G70" r:id="rId58"/>
+    <hyperlink ref="G71" r:id="rId59"/>
+    <hyperlink ref="G72" r:id="rId60"/>
+    <hyperlink ref="G73" r:id="rId61"/>
+    <hyperlink ref="G74" r:id="rId62"/>
+    <hyperlink ref="G75" r:id="rId63"/>
+    <hyperlink ref="G76" r:id="rId64"/>
+    <hyperlink ref="G77" r:id="rId65"/>
+    <hyperlink ref="G78" r:id="rId66"/>
+    <hyperlink ref="G79" r:id="rId67"/>
+    <hyperlink ref="G80" r:id="rId68"/>
+    <hyperlink ref="G81" r:id="rId69"/>
+    <hyperlink ref="G82" r:id="rId70"/>
+    <hyperlink ref="G83" r:id="rId71"/>
+    <hyperlink ref="G84" r:id="rId72"/>
+    <hyperlink ref="G85" r:id="rId73"/>
+    <hyperlink ref="G86" r:id="rId74"/>
+    <hyperlink ref="G87" r:id="rId75"/>
+    <hyperlink ref="G88" r:id="rId76"/>
+    <hyperlink ref="G89" r:id="rId77"/>
+    <hyperlink ref="G90" r:id="rId78"/>
+    <hyperlink ref="G91" r:id="rId79"/>
+    <hyperlink ref="G92" r:id="rId80"/>
+    <hyperlink ref="G93" r:id="rId81"/>
+    <hyperlink ref="G94" r:id="rId82"/>
+    <hyperlink ref="G95" r:id="rId83"/>
+    <hyperlink ref="G96" r:id="rId84"/>
+    <hyperlink ref="G97" r:id="rId85"/>
+    <hyperlink ref="G98" r:id="rId86"/>
+    <hyperlink ref="G99" r:id="rId87"/>
+    <hyperlink ref="G100" r:id="rId88"/>
+    <hyperlink ref="G101" r:id="rId89"/>
+    <hyperlink ref="G104" r:id="rId90"/>
+    <hyperlink ref="G105" r:id="rId91"/>
+    <hyperlink ref="G106" r:id="rId92"/>
+    <hyperlink ref="G107" r:id="rId93"/>
+    <hyperlink ref="G108" r:id="rId94" location="d=[[PNX_MANUSCRIPTS990000800110205171-1,FL50442639]]"/>
+    <hyperlink ref="G109" r:id="rId95" location="d=[[PNX_MANUSCRIPTS990000800110205171-1,FL50442638]]"/>
+    <hyperlink ref="G110" r:id="rId96" location="d=[[PNX_MANUSCRIPTS990000800110205171-1,FL50442638]]"/>
+    <hyperlink ref="G111" r:id="rId97" location="d=[[PNX_MANUSCRIPTS990000800110205171-1,FL50442738]]"/>
+    <hyperlink ref="G112" r:id="rId98" location="d=[[PNX_MANUSCRIPTS990001264630205171-2,FL48276986]]"/>
+    <hyperlink ref="G113" r:id="rId99" location="d=[[PNX_MANUSCRIPTS990001264630205171-2,FL48276991]]"/>
+    <hyperlink ref="G114" r:id="rId100" location="d=[[PNX_MANUSCRIPTS990001264630205171-2,FL48276997]]"/>
+    <hyperlink ref="G115" r:id="rId101" location="d=[[PNX_MANUSCRIPTS990001264630205171-2,FL48277003]]"/>
+    <hyperlink ref="G116" r:id="rId102"/>
+    <hyperlink ref="G117" r:id="rId103"/>
+    <hyperlink ref="G118" r:id="rId104"/>
+    <hyperlink ref="G119" r:id="rId105"/>
+    <hyperlink ref="G123" r:id="rId106" location="d=[[PNX_MANUSCRIPTS990001517870205171-1,FL49943073]]"/>
+    <hyperlink ref="G124" r:id="rId107" location="d=[[PNX_MANUSCRIPTS990001517870205171-1,FL49943074]]"/>
+    <hyperlink ref="G125" r:id="rId108" location="d=[[PNX_MANUSCRIPTS990001517870205171-1,FL49943075]]"/>
+    <hyperlink ref="G126" r:id="rId109" location="d=[[PNX_MANUSCRIPTS990001517870205171-1,FL49943611]]"/>
+    <hyperlink ref="G127" r:id="rId110"/>
+    <hyperlink ref="G128" r:id="rId111"/>
+    <hyperlink ref="G129" r:id="rId112"/>
+    <hyperlink ref="G130" r:id="rId113"/>
+    <hyperlink ref="G131" r:id="rId114" location="d=[[PNX_MANUSCRIPTS990001978950205171-1,FL50769309]]"/>
+    <hyperlink ref="G132" r:id="rId115" location="d=[[PNX_MANUSCRIPTS990001978950205171-1,FL50769310]]"/>
+    <hyperlink ref="G133" r:id="rId116" location="d=[[PNX_MANUSCRIPTS990001978950205171-1,FL50769311]]"/>
+    <hyperlink ref="G134" r:id="rId117" location="d=[[PNX_MANUSCRIPTS990001978950205171-1,FL50769312]]"/>
+    <hyperlink ref="G135" r:id="rId118"/>
+    <hyperlink ref="G136" r:id="rId119"/>
+    <hyperlink ref="G137" r:id="rId120"/>
+    <hyperlink ref="G138" r:id="rId121"/>
+    <hyperlink ref="G139" r:id="rId122"/>
+    <hyperlink ref="G140" r:id="rId123"/>
+    <hyperlink ref="G141" r:id="rId124"/>
+    <hyperlink ref="G142" r:id="rId125"/>
+    <hyperlink ref="G148" r:id="rId126"/>
+    <hyperlink ref="G149" r:id="rId127"/>
+    <hyperlink ref="G150" r:id="rId128"/>
+    <hyperlink ref="G151" r:id="rId129"/>
+    <hyperlink ref="G152" r:id="rId130"/>
+    <hyperlink ref="G153" r:id="rId131"/>
+    <hyperlink ref="G154" r:id="rId132"/>
+    <hyperlink ref="G155" r:id="rId133"/>
+    <hyperlink ref="G156" r:id="rId134"/>
+    <hyperlink ref="G157" r:id="rId135"/>
+    <hyperlink ref="G158" r:id="rId136"/>
+    <hyperlink ref="G159" r:id="rId137"/>
+    <hyperlink ref="G160" r:id="rId138"/>
+    <hyperlink ref="G161" r:id="rId139"/>
+    <hyperlink ref="G162" r:id="rId140"/>
+    <hyperlink ref="G163" r:id="rId141"/>
+    <hyperlink ref="G164" r:id="rId142"/>
+    <hyperlink ref="G165" r:id="rId143"/>
+    <hyperlink ref="G166" r:id="rId144"/>
+    <hyperlink ref="G167" r:id="rId145"/>
+    <hyperlink ref="G168" r:id="rId146"/>
+    <hyperlink ref="G169" r:id="rId147"/>
+    <hyperlink ref="G170" r:id="rId148"/>
+    <hyperlink ref="G171" r:id="rId149"/>
+    <hyperlink ref="G173" r:id="rId150"/>
+    <hyperlink ref="G174" r:id="rId151"/>
+    <hyperlink ref="G175" r:id="rId152"/>
+    <hyperlink ref="G176" r:id="rId153"/>
+    <hyperlink ref="G177" r:id="rId154" location="d=[[PNX_MANUSCRIPTS990025709670205171-1,FL14822146]]"/>
+    <hyperlink ref="G178" r:id="rId155" location="d=[[PNX_MANUSCRIPTS990025709670205171-1,FL14822227]]"/>
+    <hyperlink ref="G179" r:id="rId156" location="d=[[PNX_MANUSCRIPTS990025709670205171-1,FL14822061]]"/>
+    <hyperlink ref="G180" r:id="rId157" location="d=[[PNX_MANUSCRIPTS990025709670205171-1,FL14822187]]"/>
+    <hyperlink ref="G182" r:id="rId158" location="d=[[PNX_MANUSCRIPTS990000841690205171-1,FL13940557]]"/>
+    <hyperlink ref="G183" r:id="rId159" location="d=[[PNX_MANUSCRIPTS990000841690205171-1,FL13940568]]"/>
+    <hyperlink ref="G184" r:id="rId160" location="d=[[PNX_MANUSCRIPTS990000841690205171-1,FL13940717]]"/>
+    <hyperlink ref="G185" r:id="rId161" location="d=[[PNX_MANUSCRIPTS990000841690205171-1,FL13940405]]"/>
+    <hyperlink ref="G186" r:id="rId162" location="d=[[PNX_MANUSCRIPTS990000830080205171-1,FL21133815]]"/>
+    <hyperlink ref="G187" r:id="rId163" location="d=[[PNX_MANUSCRIPTS990000830080205171-1,FL21133862]]"/>
+    <hyperlink ref="G188" r:id="rId164" location="d=[[PNX_MANUSCRIPTS990000830080205171-1,FL21133861]]"/>
+    <hyperlink ref="G189" r:id="rId165" location="d=[[PNX_MANUSCRIPTS990000830080205171-1,FL21133823]]"/>
+    <hyperlink ref="G190" r:id="rId166" location="d=[[PNX_MANUSCRIPTS990000690070205171-1,FL21117134]]"/>
+    <hyperlink ref="G191" r:id="rId167" location="d=[[PNX_MANUSCRIPTS990000690070205171-1,FL21117057]]"/>
+    <hyperlink ref="G192" r:id="rId168" location="d=[[PNX_MANUSCRIPTS990000690070205171-1,FL21117713]]"/>
+    <hyperlink ref="G193" r:id="rId169" location="d=[[PNX_MANUSCRIPTS990000690070205171-1,FL21117069]]"/>
+    <hyperlink ref="G194" r:id="rId170" location="d=[[PNX_MANUSCRIPTS990000728040205171-1,FL22949894]]"/>
+    <hyperlink ref="G195" r:id="rId171" location="d=[[PNX_MANUSCRIPTS990000728040205171-1,FL22949849]]"/>
+    <hyperlink ref="G196" r:id="rId172" location="d=[[PNX_MANUSCRIPTS990000728040205171-1,FL22949980]]"/>
+    <hyperlink ref="G197" r:id="rId173" location="d=[[PNX_MANUSCRIPTS990000728040205171-1,FL22950162]]"/>
+    <hyperlink ref="G198" r:id="rId174"/>
+    <hyperlink ref="G199" r:id="rId175"/>
+    <hyperlink ref="G200" r:id="rId176"/>
+    <hyperlink ref="G201" r:id="rId177"/>
+    <hyperlink ref="G202" r:id="rId178"/>
+    <hyperlink ref="G206" r:id="rId179"/>
+    <hyperlink ref="G210" r:id="rId180"/>
   </hyperlinks>
-  <drawing r:id="rId181"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>